--- a/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41D71F8A-9624-44BA-9714-1E3B25BA153C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{753A2260-61AA-419F-8454-03B439A380CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{733EF44B-E242-49BE-9579-2E553C801C56}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3537383E-C2C6-41FE-AC44-F9B685BB6884}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2488,7 +2488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B099A6-17FD-415B-9D3B-93245CAF4B3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3A371B-75AE-4990-B796-28599F422901}">
   <dimension ref="B3:L320"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{753A2260-61AA-419F-8454-03B439A380CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEE557E-B341-4211-A217-88027BF1388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3537383E-C2C6-41FE-AC44-F9B685BB6884}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{56575710-5119-4FC9-8494-7F7BF23029C1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2488,7 +2488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3A371B-75AE-4990-B796-28599F422901}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14B795C-C3C8-430F-806F-2A04451D1000}">
   <dimension ref="B3:L320"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEE557E-B341-4211-A217-88027BF1388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3215FB9F-1755-4DC7-B5D0-74D7BF68FD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{56575710-5119-4FC9-8494-7F7BF23029C1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8D314B36-E1BE-4630-A655-1D467C501EEA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2488,7 +2488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14B795C-C3C8-430F-806F-2A04451D1000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E905E8-4568-4470-B472-FD79FCBE84B8}">
   <dimension ref="B3:L320"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3215FB9F-1755-4DC7-B5D0-74D7BF68FD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D05C24-05CF-47E9-8F50-090576322A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8D314B36-E1BE-4630-A655-1D467C501EEA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{41F109F0-8F05-4BD4-9584-86EE4925D26E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2488,7 +2488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E905E8-4568-4470-B472-FD79FCBE84B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14438FA-8439-4F45-AA2E-89E10015FAA3}">
   <dimension ref="B3:L320"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
